--- a/docs/qa/upload-templates/supplier_master_upload_template.xlsx
+++ b/docs/qa/upload-templates/supplier_master_upload_template.xlsx
@@ -133,10 +133,20 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Required unique code</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Default procurement LT (required)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
         <t>Required</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Required</t>
       </text>
@@ -434,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,12 +460,57 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>name_ar</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>lead_time_days</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>reliability_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>lead_time_days</t>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>payment_terms</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>contact_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>contact_email</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>min_order_qty</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -470,12 +525,55 @@
           <t>Cairo Copper</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>68</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>نحاس القاهرة</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>68</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Net30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hassan Ali</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>h.ali@cairocopper.example</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,12 +586,55 @@
           <t>National Wire Co</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>92</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>الأسلاك الوطنية</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>92</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Net21</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sara Nabil</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sara@natwire.example</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>50</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -506,11 +647,54 @@
           <t>Nile Steel</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>85</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>صلب النيل</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>14</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Helwan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>85</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Net45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Karim Fathy</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>karim@nilesteel.example</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
   </sheetData>
